--- a/Reay_16-29-30-B4-2H_4301354722_WCR.xlsx
+++ b/Reay_16-29-30-B4-2H_4301354722_WCR.xlsx
@@ -696,22 +696,22 @@
         <v>9904.902553191489</v>
       </c>
       <c r="D12" t="n">
-        <v>555176.1489361703</v>
+        <v>555176.8936170213</v>
       </c>
       <c r="E12" t="n">
-        <v>4458404</v>
+        <v>4458403.255319149</v>
       </c>
       <c r="F12" t="n">
-        <v>4231</v>
+        <v>4233</v>
       </c>
       <c r="G12" t="n">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="H12" t="n">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="I12" t="n">
-        <v>3870</v>
+        <v>3873</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -757,22 +757,22 @@
         <v>9679.928688524591</v>
       </c>
       <c r="D13" t="n">
-        <v>552004.868852459</v>
+        <v>552005.868852459</v>
       </c>
       <c r="E13" t="n">
-        <v>4458396.770491803</v>
+        <v>4458355.770491803</v>
       </c>
       <c r="F13" t="n">
-        <v>4192</v>
+        <v>4327</v>
       </c>
       <c r="G13" t="n">
-        <v>1085</v>
+        <v>951</v>
       </c>
       <c r="H13" t="n">
-        <v>5184</v>
+        <v>5182</v>
       </c>
       <c r="I13" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -818,22 +818,22 @@
         <v>9677.67</v>
       </c>
       <c r="D14" t="n">
-        <v>551975</v>
+        <v>551976</v>
       </c>
       <c r="E14" t="n">
-        <v>4458396</v>
+        <v>4458354</v>
       </c>
       <c r="F14" t="n">
-        <v>4195</v>
+        <v>4332</v>
       </c>
       <c r="G14" t="n">
-        <v>1083</v>
+        <v>945</v>
       </c>
       <c r="H14" t="n">
-        <v>5282</v>
+        <v>5280</v>
       </c>
       <c r="I14" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
